--- a/Compititor's_Price/Mannok_Prices/Mannok_Prices_06-08-2025.xlsx
+++ b/Compititor's_Price/Mannok_Prices/Mannok_Prices_06-08-2025.xlsx
@@ -525,12 +525,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£12.62</t>
+          <t>£12.33</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£12.62</t>
+          <t>£12.33</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -567,12 +567,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£16.18</t>
+          <t>£15.75</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£16.18</t>
+          <t>£15.75</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -609,12 +609,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£16.60</t>
+          <t>£16.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£16.60</t>
+          <t>£16.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£21.08</t>
+          <t>£21.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£21.08</t>
+          <t>£21.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -777,12 +777,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£26.50</t>
+          <t>£26.40</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£26.50</t>
+          <t>£26.40</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£28.82</t>
+          <t>£28.80</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£28.82</t>
+          <t>£28.80</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£28.35</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£28.35</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£34.99</t>
+          <t>£34.90</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£34.99</t>
+          <t>£34.90</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
